--- a/docs/ServiceNow-Element-Mapping.xlsx
+++ b/docs/ServiceNow-Element-Mapping.xlsx
@@ -279,7 +279,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elements still NOT driven from ServiceNow: About page bodies (Who We Are / Mission / Vision), Legal pages (Privacy / Terms), and the About intro — see "Unused SN Fields" for the available table fields.</t>
+          <t xml:space="preserve">Elements still NOT driven from ServiceNow: Legal pages (Privacy / Terms), the About intro paragraph, and Our Values. (About "Who We Are" is now driven by u_about_us; Our Mission / Our Vision / Why Choose VTech / How We Help sections were removed.)</t>
         </is>
       </c>
     </row>
@@ -364,7 +364,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(create property)</t>
+          <t xml:space="preserve">Upcoming Cohort Batches  ⚠ MISCONFIGURED (should be an FAQ heading, e.g. Frequently Asked Questions)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -401,7 +401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(populate field)</t>
+          <t xml:space="preserve">Quick answers about our training, consulting and staffing.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -438,7 +438,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(create property — same value as home)</t>
+          <t xml:space="preserve">Upcoming Cohort Batches  ⚠ MISCONFIGURED (same property as home)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(populate field — same value as home)</t>
+          <t xml:space="preserve">Quick answers about our training, consulting and staffing. (same as home)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(populate field)</t>
+          <t xml:space="preserve">Have questions about courses, schedules, or corporate training? Reach out and we'll get back within 1 business day.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">About intro paragraph</t>
+          <t xml:space="preserve">About intro paragraph (hero copy)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(available but unused: u_about_us)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1268,19 +1268,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Unsplash stock photo URL)</t>
+          <t xml:space="preserve">Unsplash stock photo (full-width hero, right column)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who We Are — heading + body</t>
+          <t xml:space="preserve">Who We Are — heading</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(available but unused: u_who_we / u_who_we_are_body)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1305,56 +1305,56 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VTech Infotech LLC is a full-spectrum IT services company...</t>
+          <t xml:space="preserve">Who We Are</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Our Mission — heading + body</t>
+          <t xml:space="preserve">Who We Are — body (aboutWhoWeAre)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(available but unused: u_our_missio / u_our_mission_body)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Page Configurations (x_palni_servicen_1_page_configurations)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hardcoded (not from ServiceNow)</t>
+          <t xml:space="preserve">Page Config record</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">About Us (u_about_us)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(populate field + redeploy get_page_config)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">To make in-demand technology skills accessible and practical...</t>
+          <t xml:space="preserve">VTech Infotech LLC is a full-spectrum IT services company...</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Our Vision — heading + body</t>
+          <t xml:space="preserve">Our Values (6 feat cards)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(available but unused: u_our_visio / u_our_vision_body)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1379,14 +1379,14 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">To be the trusted technology partner that bridges talent and opportunity...</t>
+          <t xml:space="preserve">Outcomes First, Hands-On Always, Integrity, Growth Mindset, Mentorship, Excellence</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Our Values (6 feat cards)</t>
+          <t xml:space="preserve">CTA — "Let's Build Your Future"</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1416,7 +1416,44 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outcomes First, Hands-On Always, Integrity, Growth Mindset, Mentorship, Excellence</t>
+          <t xml:space="preserve">Talk to an Advisor (opens lead modal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our Mission / Our Vision / Why Choose VTech / How We Help</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardcoded (not from ServiceNow)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REMOVED from the About page (sections deleted per request)</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4346,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_who_we_are_body</t>
+          <t xml:space="preserve">u_our_mission_body</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -4324,14 +4361,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">About → "Who We Are" body (page currently hardcoded)</t>
+          <t xml:space="preserve">About → "Our Mission" section REMOVED from page; field unused</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_our_mission_body</t>
+          <t xml:space="preserve">u_our_vision_body</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4346,14 +4383,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">About → "Our Mission" body (hardcoded)</t>
+          <t xml:space="preserve">About → "Our Vision" section REMOVED from page; field unused</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_our_vision_body</t>
+          <t xml:space="preserve">u_why_choose_vtech_body</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -4368,14 +4405,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">About → "Our Vision" body (hardcoded)</t>
+          <t xml:space="preserve">About → "Why Choose VTech" section REMOVED from page; field unused</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_why_choose_vtech_body</t>
+          <t xml:space="preserve">u_how_we_help_body</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4390,14 +4427,14 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">About → "Why Choose VTech" (no such section on page)</t>
+          <t xml:space="preserve">About → "How We Help" section REMOVED from page; field unused</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_how_we_help_body</t>
+          <t xml:space="preserve">u_who_we_are_body</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -4412,7 +4449,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">About → "How We Help" (no such section on page)</t>
+          <t xml:space="preserve">Superseded by u_about_us (which now drives the Who We Are body); field unused</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4471,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section heading labels (About headings hardcoded)</t>
+          <t xml:space="preserve">Section heading labels — unused (About headings hardcoded; several sections removed)</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4544,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_about_us</t>
+          <t xml:space="preserve">u_support_email</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4517,19 +4554,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(empty)</t>
+          <t xml:space="preserve">support@gmail.com</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">About page intro paragraph (still hardcoded)</t>
+          <t xml:space="preserve">Duplicate — page uses property support_email instead</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_support_email</t>
+          <t xml:space="preserve">u_support_hours</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -4539,19 +4576,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">support@gmail.com</t>
+          <t xml:space="preserve">Monday - Friday, 9:00 AM - 6:00 PM IST</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duplicate — page uses property support_email instead</t>
+          <t xml:space="preserve">Duplicate — page uses property support_hours instead</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_support_hours</t>
+          <t xml:space="preserve">u_support_phone</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4561,19 +4598,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday - Friday, 9:00 AM - 6:00 PM IST</t>
+          <t xml:space="preserve">2147483647</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duplicate — page uses property support_hours instead</t>
+          <t xml:space="preserve">Duplicate — page uses property support_number instead</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_support_phone</t>
+          <t xml:space="preserve">u_corporate_training</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -4583,19 +4620,19 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2147483647</t>
+          <t xml:space="preserve">ITSM,CSM</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duplicate — page uses property support_number instead</t>
+          <t xml:space="preserve">Not used anywhere on the page</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_corporate_training</t>
+          <t xml:space="preserve">u_image / u_style / u_video_url</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4605,19 +4642,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITSM,CSM</t>
+          <t xml:space="preserve">Image / u_image / (empty)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not used anywhere on the page</t>
+          <t xml:space="preserve">Legacy hero media/style toggle (hero image now from property hero_video_url)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_image / u_style / u_video_url</t>
+          <t xml:space="preserve">u_order</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -4627,32 +4664,10 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Image / u_image / (empty)</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Legacy hero media/style toggle (hero image now from property hero_video_url)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">u_order</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page Configurations</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Record-ordering metadata (site picks the most recently updated active record)</t>
         </is>
@@ -6484,7 +6499,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(populate field)</t>
+          <t xml:space="preserve">Real feedback from learners who transformed their careers with VTech.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6558,7 +6573,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(populate field — same value as home)</t>
+          <t xml:space="preserve">Real feedback from learners who transformed their careers with VTech. (same as home)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6722,7 +6737,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(create property)</t>
+          <t xml:space="preserve">Upcoming Cohort Batches</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -6759,7 +6774,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(populate field)</t>
+          <t xml:space="preserve">Reserve your seat — new cohorts starting across our programs.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6796,7 +6811,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(create property — same value as home)</t>
+          <t xml:space="preserve">Upcoming Cohort Batches (same as home)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6833,7 +6848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(populate field — same value as home)</t>
+          <t xml:space="preserve">Reserve your seat — new cohorts starting across our programs. (same as home)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">

--- a/docs/ServiceNow-Element-Mapping.xlsx
+++ b/docs/ServiceNow-Element-Mapping.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RajKolli\GitHub Repo\ClaudeAILearning001\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7762E678-0C5E-4AFA-B4A6-C27F8219E8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E803CC5-13C8-4555-B0D4-AFCB1CBE4972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Legend" sheetId="1" r:id="rId1"/>
-    <sheet name="Nav &amp; Footer" sheetId="2" r:id="rId2"/>
-    <sheet name="Hero" sheetId="3" r:id="rId3"/>
-    <sheet name="Enterprise" sheetId="12" r:id="rId4"/>
-    <sheet name="About Us" sheetId="13" r:id="rId5"/>
+    <sheet name="Nav &amp; Footer" sheetId="2" r:id="rId1"/>
+    <sheet name="Hero" sheetId="3" r:id="rId2"/>
+    <sheet name="Enterprise" sheetId="12" r:id="rId3"/>
+    <sheet name="About Us" sheetId="13" r:id="rId4"/>
+    <sheet name="Course Detail Page" sheetId="18" r:id="rId5"/>
     <sheet name="Stats Band" sheetId="4" r:id="rId6"/>
     <sheet name="Services" sheetId="5" r:id="rId7"/>
     <sheet name="Courses" sheetId="6" r:id="rId8"/>
@@ -30,111 +30,40 @@
     <sheet name="Theme Colors" sheetId="15" r:id="rId15"/>
     <sheet name="Legal Pages" sheetId="16" r:id="rId16"/>
     <sheet name="Alumni &amp; Leads" sheetId="17" r:id="rId17"/>
-    <sheet name="Course Detail Page" sheetId="18" r:id="rId18"/>
-    <sheet name="Trainer Profile" sheetId="19" r:id="rId19"/>
-    <sheet name="Modals &amp; Forms" sheetId="20" r:id="rId20"/>
-    <sheet name="Unused SN Fields" sheetId="21" r:id="rId21"/>
+    <sheet name="Trainer Profile" sheetId="19" r:id="rId18"/>
+    <sheet name="Modals &amp; Forms" sheetId="20" r:id="rId19"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="483">
-  <si>
-    <t>Column / term</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="415">
   <si>
     <t>Webpage Element (backend id)</t>
   </si>
   <si>
-    <t>Human-readable element + its HTML id / backend hook</t>
-  </si>
-  <si>
     <t>Property Description (property name)</t>
   </si>
   <si>
-    <t>Filled when the element is driven by a ServiceNow System Property (sys_properties)</t>
-  </si>
-  <si>
     <t>Table label (name)</t>
   </si>
   <si>
-    <t>Filled when the element is driven by a ServiceNow table</t>
-  </si>
-  <si>
     <t>Driven by Record / Field</t>
   </si>
   <si>
-    <t>What supplies the value (see driver types below)</t>
-  </si>
-  <si>
     <t>Field label (name)</t>
   </si>
   <si>
-    <t>The driving table field(s): label (u_field_name)</t>
-  </si>
-  <si>
     <t>Current value</t>
   </si>
   <si>
-    <t>Live value fetched from ServiceNow on 2026-07-03</t>
-  </si>
-  <si>
     <t>Default value</t>
   </si>
   <si>
-    <t>Hard-coded fallback in index.html when ServiceNow is empty/unreachable</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>Driver: System Property</t>
-  </si>
-  <si>
-    <t>Value comes from a sys_properties record (get_properties API)</t>
-  </si>
-  <si>
-    <t>Driver: Page Config record</t>
-  </si>
-  <si>
-    <t>Value comes from the page-configurations record (get_page_config API)</t>
-  </si>
-  <si>
-    <t>Driver: Table (dynamic list)</t>
-  </si>
-  <si>
-    <t>Value comes from a table, one row per card/item</t>
-  </si>
-  <si>
-    <t>Driver: Hardcoded (not from ServiceNow)</t>
-  </si>
-  <si>
-    <t>Static text/markup in index.html — NOT driven by ServiceNow</t>
-  </si>
-  <si>
-    <t>Driver: Client-side (JS)</t>
-  </si>
-  <si>
-    <t>Computed in the browser (e.g. current year, "view all" links)</t>
-  </si>
-  <si>
-    <t>NOTE</t>
-  </si>
-  <si>
-    <t>Reviews/Cohort/FAQ/Contact subtexts are now driven by page-config fields (u_alumni_feedback_subtext, u_cohort_batches_subtext, u_faq_subtext, u_support_section_subtext). Cohort + FAQ headings need two NEW properties: x_palni_servicen_1.home_batches_section_heading and x_palni_servicen_1.faq_heading.</t>
-  </si>
-  <si>
-    <t>REMAINING GAPS</t>
-  </si>
-  <si>
-    <t>Elements still NOT driven from ServiceNow: Legal pages (Privacy / Terms), the About intro paragraph, and Our Values. (About "Who We Are" is now driven by u_about_us; Our Mission / Our Vision / Why Choose VTech / How We Help sections were removed.)</t>
-  </si>
-  <si>
     <t>Nav logo image (nav-logo img)</t>
   </si>
   <si>
@@ -1038,18 +967,12 @@
     <t>Privacy Policy page (privacyView)</t>
   </si>
   <si>
-    <t>(available but unused: u_privacy_policy)</t>
-  </si>
-  <si>
     <t>Full hardcoded Privacy Policy (10 sections)</t>
   </si>
   <si>
     <t>Terms &amp; Conditions page (termsView)</t>
   </si>
   <si>
-    <t>(available but unused: u_terms_and_conditions)</t>
-  </si>
-  <si>
     <t>Full hardcoded Terms &amp; Conditions (12 sections)</t>
   </si>
   <si>
@@ -1350,145 +1273,16 @@
     <t>fallback cards</t>
   </si>
   <si>
-    <t>Property / Field name</t>
-  </si>
-  <si>
-    <t>Status / where it could be used</t>
-  </si>
-  <si>
-    <t>— No unused system properties —</t>
-  </si>
-  <si>
-    <t>sys_properties</t>
-  </si>
-  <si>
-    <t>All 23 System Properties are in use</t>
-  </si>
-  <si>
-    <t>u_our_mission_body</t>
-  </si>
-  <si>
-    <t>Page Configurations</t>
-  </si>
-  <si>
-    <t>(HTML content)</t>
-  </si>
-  <si>
-    <t>About → "Our Mission" section REMOVED from page; field unused</t>
-  </si>
-  <si>
-    <t>u_our_vision_body</t>
-  </si>
-  <si>
-    <t>About → "Our Vision" section REMOVED from page; field unused</t>
-  </si>
-  <si>
-    <t>u_why_choose_vtech_body</t>
-  </si>
-  <si>
-    <t>About → "Why Choose VTech" section REMOVED from page; field unused</t>
-  </si>
-  <si>
-    <t>u_how_we_help_body</t>
-  </si>
-  <si>
-    <t>About → "How We Help" section REMOVED from page; field unused</t>
-  </si>
-  <si>
-    <t>u_who_we_are_body</t>
-  </si>
-  <si>
-    <t>Superseded by u_about_us (which now drives the Who We Are body); field unused</t>
-  </si>
-  <si>
-    <t>u_who_we / u_our_missio / u_our_visio / u_how_we_hel / u_why_choose_vtec</t>
-  </si>
-  <si>
-    <t>Who We Are / Our Mission / Our Vision / How We Help / Our Vision</t>
-  </si>
-  <si>
-    <t>Section heading labels — unused (About headings hardcoded; several sections removed)</t>
-  </si>
-  <si>
-    <t>u_who_we_are / u_our_mission / u_our_vision / u_how_we_help / u_why_choose_vtech</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>Section show/hide toggles (not wired)</t>
-  </si>
-  <si>
-    <t>u_privacy_policy</t>
-  </si>
-  <si>
-    <t>Privacy Policy page (currently hardcoded)</t>
-  </si>
-  <si>
-    <t>u_terms_and_conditions</t>
-  </si>
-  <si>
-    <t>Terms &amp; Conditions page (currently hardcoded)</t>
-  </si>
-  <si>
-    <t>u_support_email</t>
-  </si>
-  <si>
-    <t>support@gmail.com</t>
-  </si>
-  <si>
-    <t>Duplicate — page uses property support_email instead</t>
-  </si>
-  <si>
-    <t>u_support_hours</t>
-  </si>
-  <si>
-    <t>Monday - Friday, 9:00 AM - 6:00 PM IST</t>
-  </si>
-  <si>
-    <t>Duplicate — page uses property support_hours instead</t>
-  </si>
-  <si>
-    <t>u_support_phone</t>
-  </si>
-  <si>
-    <t>2147483647</t>
-  </si>
-  <si>
-    <t>Duplicate — page uses property support_number instead</t>
-  </si>
-  <si>
-    <t>u_corporate_training</t>
-  </si>
-  <si>
-    <t>ITSM,CSM</t>
-  </si>
-  <si>
-    <t>Not used anywhere on the page</t>
-  </si>
-  <si>
-    <t>u_image / u_style / u_video_url</t>
-  </si>
-  <si>
-    <t>Image / u_image / (empty)</t>
-  </si>
-  <si>
-    <t>Legacy hero media/style toggle (hero image now from property hero_video_url)</t>
-  </si>
-  <si>
-    <t>u_order</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Record-ordering metadata (site picks the most recently updated active record)</t>
-  </si>
-  <si>
     <t>x_palni_servicen_1.color_nav_footer</t>
   </si>
   <si>
     <t>#e8f1fb</t>
+  </si>
+  <si>
+    <t>Privacy Policy (u_privacy_policy)</t>
+  </si>
+  <si>
+    <t>Terms and Conditions (u_terms_and_conditions)</t>
   </si>
 </sst>
 </file>
@@ -1873,148 +1667,295 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="26" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="13" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="13" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="52" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="39" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>30</v>
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2040,163 +1981,163 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2222,163 +2163,163 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2404,163 +2345,163 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2586,209 +2527,209 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -2814,48 +2755,48 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -2866,7 +2807,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
@@ -2881,232 +2822,232 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>481</v>
+        <v>411</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>412</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>482</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -3116,6 +3057,9 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3129,71 +3073,67 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>332</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>413</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>335</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>414</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3203,6 +3143,9 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3216,71 +3159,71 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3289,531 +3232,10 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="7" width="46" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="39" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3827,324 +3249,324 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4152,305 +3574,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="7" width="46" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="39" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4464,163 +3592,163 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="130" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -4628,261 +3756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
@@ -4897,163 +3771,163 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5061,7 +3935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
@@ -5076,94 +3950,94 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -5171,8 +4045,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5186,212 +4063,739 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="7" width="46" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5415,140 +4819,140 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -5574,209 +4978,209 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5802,278 +5206,278 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -6099,232 +5503,232 @@
   <sheetData>
     <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ServiceNow-Element-Mapping.xlsx
+++ b/docs/ServiceNow-Element-Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RajKolli\GitHub Repo\ClaudeAILearning001\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E803CC5-13C8-4555-B0D4-AFCB1CBE4972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C49585-C7AC-404E-ACA5-F676AD1E780B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nav &amp; Footer" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="420">
   <si>
     <t>Webpage Element (backend id)</t>
   </si>
@@ -121,9 +121,6 @@
     <t>About Us / Our Courses / Our Experts</t>
   </si>
   <si>
-    <t>Footer support phone (js-support-phone)</t>
-  </si>
-  <si>
     <t>Support number (x_palni_servicen_1.support_number)</t>
   </si>
   <si>
@@ -277,9 +274,6 @@
     <t>Services mega-menu heading (servicesHeading)</t>
   </si>
   <si>
-    <t>Services heading (x_palni_servicen_1.services_heading)</t>
-  </si>
-  <si>
     <t>End-to-End IT Services</t>
   </si>
   <si>
@@ -346,9 +340,6 @@
     <t>Courses heading — home (coursesHeading)</t>
   </si>
   <si>
-    <t>Courses heading (x_palni_servicen_1.home_course_main_heading)</t>
-  </si>
-  <si>
     <t>In-Demand Career Courses</t>
   </si>
   <si>
@@ -370,9 +361,6 @@
     <t>Courses page heading (coursesPageHeading)</t>
   </si>
   <si>
-    <t>Reuses Courses heading (x_palni_servicen_1.home_course_main_heading)</t>
-  </si>
-  <si>
     <t>Our Courses</t>
   </si>
   <si>
@@ -451,9 +439,6 @@
     <t>Trainers heading — home (trainersPreviewHeading)</t>
   </si>
   <si>
-    <t>Trainers heading (x_palni_servicen_1.home_trainers_main_heading)</t>
-  </si>
-  <si>
     <t>Meet Your Expert Instructors</t>
   </si>
   <si>
@@ -475,9 +460,6 @@
     <t>Trainers page heading (trainersPageHeading)</t>
   </si>
   <si>
-    <t>Reuses Trainers heading (x_palni_servicen_1.home_trainers_main_heading)</t>
-  </si>
-  <si>
     <t>Meet Our Trainers</t>
   </si>
   <si>
@@ -532,9 +514,6 @@
     <t>Reviews heading — home (feedbackHeading)</t>
   </si>
   <si>
-    <t>Reviews heading (x_palni_servicen_1.home_feedback_main_heading)</t>
-  </si>
-  <si>
     <t>Stories from Our Alumni</t>
   </si>
   <si>
@@ -553,9 +532,6 @@
     <t>Reviews page heading</t>
   </si>
   <si>
-    <t>Reuses Reviews heading (x_palni_servicen_1.home_feedback_main_heading)</t>
-  </si>
-  <si>
     <t>Reviews &amp; Feedback</t>
   </si>
   <si>
@@ -577,9 +553,6 @@
     <t>Table — one row per review</t>
   </si>
   <si>
-    <t>Comment (u_comment), Overall (u_overall_rating), Trainer (u_trainer), Trainee (u_trainee) + sub-ratings</t>
-  </si>
-  <si>
     <t>(from get_trainee_feedback)</t>
   </si>
   <si>
@@ -601,9 +574,6 @@
     <t>Home batches heading (batchesHeading)</t>
   </si>
   <si>
-    <t>Cohort batches heading (x_palni_servicen_1.home_batches_section_heading)</t>
-  </si>
-  <si>
     <t>Upcoming Cohort Batches</t>
   </si>
   <si>
@@ -619,9 +589,6 @@
     <t>Cohorts page heading (cohortsPageHeading)</t>
   </si>
   <si>
-    <t>Reuses Cohort batches heading (x_palni_servicen_1.home_batches_section_heading)</t>
-  </si>
-  <si>
     <t>Upcoming Cohort Batches (same as home)</t>
   </si>
   <si>
@@ -661,12 +628,6 @@
     <t>Home FAQ heading (faqHeading)</t>
   </si>
   <si>
-    <t>FAQ heading (x_palni_servicen_1.faq_heading)</t>
-  </si>
-  <si>
-    <t>Upcoming Cohort Batches  ⚠ MISCONFIGURED (should be an FAQ heading, e.g. Frequently Asked Questions)</t>
-  </si>
-  <si>
     <t>Frequently Asked Questions</t>
   </si>
   <si>
@@ -682,12 +643,6 @@
     <t>FAQ page heading (faqPageHeading)</t>
   </si>
   <si>
-    <t>Reuses FAQ heading (x_palni_servicen_1.faq_heading)</t>
-  </si>
-  <si>
-    <t>Upcoming Cohort Batches  ⚠ MISCONFIGURED (same property as home)</t>
-  </si>
-  <si>
     <t>FAQ page subtext (faqPageSubheading)</t>
   </si>
   <si>
@@ -724,9 +679,6 @@
     <t>Contact heading (supportHeading)</t>
   </si>
   <si>
-    <t>Support heading (x_palni_servicen_1.support_main_heading)</t>
-  </si>
-  <si>
     <t>Get Personalized Career Guidance</t>
   </si>
   <si>
@@ -736,9 +688,6 @@
     <t>Contact subheading (supportSubheading)</t>
   </si>
   <si>
-    <t>Contact/Support Subtext (u_support_section_subtext)</t>
-  </si>
-  <si>
     <t>Have questions about courses, schedules, or corporate training? Reach out and we'll get back within 1 business day.</t>
   </si>
   <si>
@@ -799,9 +748,6 @@
     <t>Enterprise heading (enterpriseHeading)</t>
   </si>
   <si>
-    <t>Enterprise heading (x_palni_servicen_1.enterprise_section_heading)</t>
-  </si>
-  <si>
     <t>Are you an enterprise looking to upskill your employees?</t>
   </si>
   <si>
@@ -826,9 +772,6 @@
     <t>About page H1 (aboutHeading)</t>
   </si>
   <si>
-    <t>About Us heading (x_palni_servicen_1.about_us_heading)</t>
-  </si>
-  <si>
     <t>About eyebrow label</t>
   </si>
   <si>
@@ -994,9 +937,6 @@
     <t>POST → register_lead</t>
   </si>
   <si>
-    <t>Name, email, phone, course, source</t>
-  </si>
-  <si>
     <t>Back to Courses link</t>
   </si>
   <si>
@@ -1231,9 +1171,6 @@
     <t>Lead / "Book a Free Demo" modal — fields</t>
   </si>
   <si>
-    <t>Name, Email, Phone, Course, Message, Source</t>
-  </si>
-  <si>
     <t>(user input)</t>
   </si>
   <si>
@@ -1255,9 +1192,6 @@
     <t>POST → post_trainee_feedback</t>
   </si>
   <si>
-    <t>Trainer, Trainee, Batch, Comment + rating sliders (u_overall_rating, u_depth_of_knowledge_covered, u_clarity_of_explanation, u_interaction_with_participants, u_hands_on_experience, u_real_world_examples, u_session_planning_and_flow, u_mentorship_and_guidance, u_likelihood_to_recommend_this_program)</t>
-  </si>
-  <si>
     <t>Review sort dropdown</t>
   </si>
   <si>
@@ -1283,6 +1217,87 @@
   </si>
   <si>
     <t>Terms and Conditions (u_terms_and_conditions)</t>
+  </si>
+  <si>
+    <t>Courses (x_palni_servicen_1_course_offerings)</t>
+  </si>
+  <si>
+    <t>Courses Heading (u_courses_heading)</t>
+  </si>
+  <si>
+    <t>Page Config record (same field as home)</t>
+  </si>
+  <si>
+    <t>Trainers Heading (u_trainers_heading)</t>
+  </si>
+  <si>
+    <t>Feedback Heading (u_feedback_heading)</t>
+  </si>
+  <si>
+    <t>Cohort Batches Heading (u_cohort_batches_heading)</t>
+  </si>
+  <si>
+    <t>FAQ Heading (u_faq_heading)</t>
+  </si>
+  <si>
+    <t>Enterprise Heading (u_enterprise_heading)</t>
+  </si>
+  <si>
+    <t>About Us Heading (u_about_us_heading)</t>
+  </si>
+  <si>
+    <t>Services Heading (u_services_heading)</t>
+  </si>
+  <si>
+    <t>Support Section Heading (u_support_section_heading)</t>
+  </si>
+  <si>
+    <t>Support Section Subtext (u_support_section_subtext)</t>
+  </si>
+  <si>
+    <t>Short Bio (u_short_bio)</t>
+  </si>
+  <si>
+    <t>Short bio / home card blurb (u_short_bio)</t>
+  </si>
+  <si>
+    <t>Resume (sys_attachment via resume_id, resume_name)</t>
+  </si>
+  <si>
+    <t>Resume download (resume_id / resume_name)</t>
+  </si>
+  <si>
+    <t>Download button shown only when resume_id is set</t>
+  </si>
+  <si>
+    <t>Trainer card — short bio (home portrait card)</t>
+  </si>
+  <si>
+    <t>Shown under name on home portrait card</t>
+  </si>
+  <si>
+    <t>Name (u_full_name), Email (u_email), Phone (u_phone), Company (u_company), Course (u_course_of_interest), Mode (u_preferred_mode), Preferred Date (u_preferred_date), Preferred Time (u_preferred_time), Time Zone (u_time_zone), Message (u_message), Source (class)</t>
+  </si>
+  <si>
+    <t>Name (u_full_name), Email (u_email), Phone with country code (u_phone), Company (u_company), Course of Interest (u_course_of_interest), Preferred Mode (u_preferred_mode), Preferred Date (u_preferred_date), Preferred Time (u_preferred_time), Time Zone / IANA (u_time_zone), Message (u_message), Source/CTA label (class)</t>
+  </si>
+  <si>
+    <t>Trainee (u_trainee), Trainer (u_trainer), Batch (u_batch), Comment (u_comment), Posted On (u_posted_on), Overall Rating (u_overall_rating), Depth of Knowledge (u_depth_of_knowledge_covered), Clarity of Explanation (u_clarity_of_explanation), Interaction with Participants (u_interaction_with_participants), Hands-On Experience (u_hands_on_experience), Real-World Examples (u_real_world_examples), Session Planning (u_session_planning_and_flow), Mentorship (u_mentorship_and_guidance), Likelihood to Recommend (u_likelihood_to_recommend_this_program)</t>
+  </si>
+  <si>
+    <t>Trainer (u_trainer), Trainee (u_trainee), Batch (u_batch), Comment (u_comment), Overall Rating (u_overall_rating), Depth of Knowledge (u_depth_of_knowledge_covered), Clarity of Explanation (u_clarity_of_explanation), Interaction (u_interaction_with_participants), Hands-On Experience (u_hands_on_experience), Real-World Examples (u_real_world_examples), Session Planning (u_session_planning_and_flow), Mentorship (u_mentorship_and_guidance), Likelihood to Recommend (u_likelihood_to_recommend_this_program)</t>
+  </si>
+  <si>
+    <t>Footer support phone + call/WhatsApp FABs (.js-support-phone, waBubble)</t>
+  </si>
+  <si>
+    <t>System ID (sys_id) — used to build /course_image/{sys_id} and /course_curriculum/{sys_id} URLs</t>
+  </si>
+  <si>
+    <t>Course image (src on &lt;img&gt;) and curriculum download</t>
+  </si>
+  <si>
+    <t>Image loaded via &lt;img src&gt; directly; curriculum streamed as binary download after lead form</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1687,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1682,7 +1697,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1914,48 +1929,48 @@
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1969,7 +1984,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1979,7 +1994,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2002,139 +2017,135 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>164</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>171</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>395</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="195" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="39" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>7</v>
@@ -2151,7 +2162,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2161,7 +2172,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2184,124 +2195,120 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>187</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>193</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>395</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -2310,13 +2317,13 @@
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>7</v>
@@ -2333,7 +2340,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2343,7 +2350,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2366,124 +2373,120 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>207</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>399</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>214</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>395</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>399</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -2492,13 +2495,13 @@
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>7</v>
@@ -2515,7 +2518,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2525,7 +2528,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2548,162 +2551,158 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>403</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>232</v>
+        <v>404</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>7</v>
@@ -2711,25 +2710,25 @@
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2743,7 +2742,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2753,7 +2752,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2778,25 +2777,25 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2810,7 +2809,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -2820,7 +2819,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2843,211 +2842,211 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="B10" s="2" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -3061,7 +3060,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3071,7 +3070,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3096,44 +3095,44 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>413</v>
+        <v>391</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3147,7 +3146,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3157,7 +3156,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3182,45 +3181,45 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" ht="104" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>318</v>
+        <v>412</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>7</v>
@@ -3236,8 +3235,8 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3247,7 +3246,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3272,42 +3271,42 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -3318,19 +3317,19 @@
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>7</v>
@@ -3341,19 +3340,19 @@
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
@@ -3364,19 +3363,19 @@
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>7</v>
@@ -3387,19 +3386,19 @@
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
@@ -3410,19 +3409,19 @@
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
@@ -3433,19 +3432,19 @@
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
@@ -3456,19 +3455,19 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
@@ -3479,76 +3478,70 @@
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>388</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>7</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>7</v>
+        <v>370</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>392</v>
+        <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -3557,15 +3550,57 @@
         <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3580,7 +3615,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3590,7 +3625,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3613,47 +3648,47 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="117" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>7</v>
@@ -3661,7 +3696,7 @@
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -3679,35 +3714,35 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="130" x14ac:dyDescent="0.3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="195" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -3716,39 +3751,39 @@
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3794,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3769,7 +3804,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3794,76 +3829,76 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -3881,35 +3916,35 @@
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -3927,7 +3962,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3938,7 +3973,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3948,7 +3983,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3971,55 +4006,53 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>253</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -4037,7 +4070,7 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4050,8 +4083,8 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4061,7 +4094,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4086,30 +4119,28 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>262</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>401</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -4127,12 +4158,12 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -4150,12 +4181,12 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -4173,12 +4204,12 @@
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -4196,35 +4227,35 @@
         <v>7</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
@@ -4242,12 +4273,12 @@
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
@@ -4265,10 +4296,9 @@
         <v>7</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3"/>
+        <v>259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4280,7 +4310,7 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4290,7 +4320,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4315,7 +4345,7 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -4333,150 +4363,150 @@
         <v>7</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
@@ -4485,56 +4515,56 @@
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>7</v>
@@ -4545,19 +4575,19 @@
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>7</v>
@@ -4568,19 +4598,19 @@
     </row>
     <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>7</v>
@@ -4591,19 +4621,19 @@
     </row>
     <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>7</v>
@@ -4614,91 +4644,91 @@
     </row>
     <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>7</v>
@@ -4706,76 +4736,76 @@
     </row>
     <row r="19" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
@@ -4793,7 +4823,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4807,7 +4837,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4817,7 +4847,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4842,117 +4872,117 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -4966,7 +4996,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -4976,7 +5006,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5001,180 +5031,178 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
@@ -5193,8 +5221,8 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5204,7 +5232,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5227,136 +5255,132 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
@@ -5367,19 +5391,19 @@
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
@@ -5390,19 +5414,19 @@
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
@@ -5413,19 +5437,19 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
@@ -5434,21 +5458,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>7</v>
@@ -5459,25 +5483,44 @@
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>135</v>
+    </row>
+    <row r="13" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5490,8 +5533,8 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -5501,7 +5544,7 @@
     <col min="6" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5524,136 +5567,132 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>137</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>396</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="39" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
@@ -5664,19 +5703,19 @@
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
@@ -5687,19 +5726,19 @@
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
@@ -5710,24 +5749,43 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/docs/ServiceNow-Element-Mapping.xlsx
+++ b/docs/ServiceNow-Element-Mapping.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C49585-C7AC-404E-ACA5-F676AD1E780B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nav &amp; Footer" sheetId="2" r:id="rId1"/>

--- a/docs/ServiceNow-Element-Mapping.xlsx
+++ b/docs/ServiceNow-Element-Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RajKolli\GitHub Repo\ClaudeAILearning001\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C49585-C7AC-404E-ACA5-F676AD1E780B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01439290-365D-4309-8B4A-34664D819EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="421">
   <si>
     <t>Webpage Element (backend id)</t>
   </si>
@@ -985,12 +985,6 @@
     <t>client-side toggle</t>
   </si>
   <si>
-    <t>Highlights / What you'll learn</t>
-  </si>
-  <si>
-    <t>Highlights (u_highlights, split by ".")</t>
-  </si>
-  <si>
     <t>Details coming soon.</t>
   </si>
   <si>
@@ -1298,6 +1292,15 @@
   </si>
   <si>
     <t>Image loaded via &lt;img src&gt; directly; curriculum streamed as binary download after lead form</t>
+  </si>
+  <si>
+    <t>Course Features</t>
+  </si>
+  <si>
+    <t>Course Features (u_highlights, split by ".")</t>
+  </si>
+  <si>
+    <t>Courses (x_palni_servicen_1_cou+E12+C16</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +1932,7 @@
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -2029,7 +2032,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>158</v>
@@ -2070,10 +2073,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>158</v>
@@ -2119,7 +2122,7 @@
         <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>171</v>
@@ -2207,7 +2210,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>178</v>
@@ -2248,10 +2251,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>183</v>
@@ -2385,7 +2388,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>196</v>
@@ -2426,10 +2429,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>196</v>
@@ -2563,7 +2566,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>213</v>
@@ -2584,7 +2587,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>216</v>
@@ -3031,7 +3034,7 @@
         <v>288</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
@@ -3043,10 +3046,10 @@
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3105,7 +3108,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
@@ -3126,7 +3129,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -3216,7 +3219,7 @@
         <v>298</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>176</v>
@@ -3271,7 +3274,7 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -3289,12 +3292,12 @@
         <v>147</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -3306,7 +3309,7 @@
         <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -3317,7 +3320,7 @@
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -3329,7 +3332,7 @@
         <v>116</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>7</v>
@@ -3340,7 +3343,7 @@
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -3352,7 +3355,7 @@
         <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
@@ -3363,7 +3366,7 @@
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -3375,7 +3378,7 @@
         <v>116</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>7</v>
@@ -3386,7 +3389,7 @@
     </row>
     <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -3398,7 +3401,7 @@
         <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
@@ -3409,7 +3412,7 @@
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
@@ -3421,7 +3424,7 @@
         <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
@@ -3432,7 +3435,7 @@
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
@@ -3444,7 +3447,7 @@
         <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
@@ -3455,7 +3458,7 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
@@ -3467,7 +3470,7 @@
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
@@ -3478,7 +3481,7 @@
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
@@ -3488,14 +3491,14 @@
         <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -3507,18 +3510,18 @@
         <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -3530,7 +3533,7 @@
         <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>7</v>
@@ -3541,7 +3544,7 @@
     </row>
     <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -3556,15 +3559,15 @@
         <v>7</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
@@ -3574,16 +3577,16 @@
         <v>116</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
@@ -3598,7 +3601,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>7</v>
@@ -3650,7 +3653,7 @@
     </row>
     <row r="2" spans="1:7" ht="117" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -3662,10 +3665,10 @@
         <v>298</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>302</v>
@@ -3673,7 +3676,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -3685,7 +3688,7 @@
         <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>113</v>
@@ -3696,7 +3699,7 @@
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -3714,12 +3717,12 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="195" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -3728,13 +3731,13 @@
         <v>169</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>302</v>
@@ -3742,7 +3745,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -3757,7 +3760,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>7</v>
@@ -3765,7 +3768,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -3777,13 +3780,13 @@
         <v>85</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -4018,7 +4021,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>236</v>
@@ -4129,7 +4132,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>55</v>
@@ -4374,7 +4377,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>116</v>
@@ -4397,7 +4400,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>116</v>
@@ -4420,7 +4423,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>116</v>
@@ -4443,7 +4446,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>116</v>
@@ -4466,7 +4469,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>116</v>
@@ -4489,7 +4492,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>116</v>
@@ -4529,42 +4532,42 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>315</v>
+        <v>418</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>316</v>
+        <v>419</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>7</v>
@@ -4575,19 +4578,19 @@
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>7</v>
@@ -4598,19 +4601,19 @@
     </row>
     <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>7</v>
@@ -4621,19 +4624,19 @@
     </row>
     <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>7</v>
@@ -4644,65 +4647,65 @@
     </row>
     <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>128</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>130</v>
@@ -4713,22 +4716,22 @@
     </row>
     <row r="18" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>7</v>
@@ -4736,7 +4739,7 @@
     </row>
     <row r="19" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>7</v>
@@ -4745,10 +4748,10 @@
         <v>188</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>191</v>
@@ -4759,7 +4762,7 @@
     </row>
     <row r="20" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
@@ -4771,18 +4774,18 @@
         <v>116</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>208</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>7</v>
@@ -4794,18 +4797,18 @@
         <v>116</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
@@ -4823,7 +4826,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5041,7 +5044,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>78</v>
@@ -5267,7 +5270,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>100</v>
@@ -5308,10 +5311,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>100</v>
@@ -5331,7 +5334,7 @@
         <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>103</v>
@@ -5351,7 +5354,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>111</v>
@@ -5374,7 +5377,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>116</v>
@@ -5397,7 +5400,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>116</v>
@@ -5420,7 +5423,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>116</v>
@@ -5443,7 +5446,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>116</v>
@@ -5466,7 +5469,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>116</v>
@@ -5506,21 +5509,21 @@
     </row>
     <row r="13" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5579,7 +5582,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>133</v>
@@ -5620,10 +5623,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>133</v>
@@ -5749,7 +5752,7 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
@@ -5759,11 +5762,11 @@
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">

--- a/docs/ServiceNow-Element-Mapping.xlsx
+++ b/docs/ServiceNow-Element-Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RajKolli\GitHub Repo\ClaudeAILearning001\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01439290-365D-4309-8B4A-34664D819EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA23BD0-CD24-4D87-A24F-1ECF9D285A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nav &amp; Footer" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="419">
   <si>
     <t>Webpage Element (backend id)</t>
   </si>
@@ -998,12 +998,6 @@
   </si>
   <si>
     <t>Prerequisites (u_pre_requisites, comma-separated)</t>
-  </si>
-  <si>
-    <t>Who should attend / participants</t>
-  </si>
-  <si>
-    <t>Participants (u_participants_trained, comma-separated)</t>
   </si>
   <si>
     <t>Learning journey (animated steps)</t>
@@ -1932,7 +1926,7 @@
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>27</v>
@@ -2032,7 +2026,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>158</v>
@@ -2073,10 +2067,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>158</v>
@@ -2122,7 +2116,7 @@
         <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>171</v>
@@ -2210,7 +2204,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>178</v>
@@ -2251,10 +2245,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>183</v>
@@ -2388,7 +2382,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>196</v>
@@ -2429,10 +2423,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>196</v>
@@ -2566,7 +2560,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>213</v>
@@ -2587,7 +2581,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>216</v>
@@ -3034,7 +3028,7 @@
         <v>288</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
@@ -3046,10 +3040,10 @@
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3108,7 +3102,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
@@ -3129,7 +3123,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -3219,7 +3213,7 @@
         <v>298</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>176</v>
@@ -3274,7 +3268,7 @@
     </row>
     <row r="2" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -3292,12 +3286,12 @@
         <v>147</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -3309,7 +3303,7 @@
         <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -3320,7 +3314,7 @@
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -3332,7 +3326,7 @@
         <v>116</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>7</v>
@@ -3343,7 +3337,7 @@
     </row>
     <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -3355,7 +3349,7 @@
         <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
@@ -3366,7 +3360,7 @@
     </row>
     <row r="6" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -3378,7 +3372,7 @@
         <v>116</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>7</v>
@@ -3401,7 +3395,7 @@
         <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
@@ -3412,7 +3406,7 @@
     </row>
     <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
@@ -3424,7 +3418,7 @@
         <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
@@ -3435,7 +3429,7 @@
     </row>
     <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
@@ -3447,7 +3441,7 @@
         <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
@@ -3458,7 +3452,7 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
@@ -3470,7 +3464,7 @@
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
@@ -3481,7 +3475,7 @@
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
@@ -3491,14 +3485,14 @@
         <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -3510,18 +3504,18 @@
         <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -3533,7 +3527,7 @@
         <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>7</v>
@@ -3544,7 +3538,7 @@
     </row>
     <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -3559,15 +3553,15 @@
         <v>7</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
@@ -3577,16 +3571,16 @@
         <v>116</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
@@ -3601,7 +3595,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>7</v>
@@ -3653,7 +3647,7 @@
     </row>
     <row r="2" spans="1:7" ht="117" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -3665,10 +3659,10 @@
         <v>298</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>302</v>
@@ -3676,7 +3670,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -3688,7 +3682,7 @@
         <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>113</v>
@@ -3699,7 +3693,7 @@
     </row>
     <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -3717,12 +3711,12 @@
         <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="195" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -3731,13 +3725,13 @@
         <v>169</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>302</v>
@@ -3745,7 +3739,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -3760,7 +3754,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>7</v>
@@ -3768,7 +3762,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -3780,13 +3774,13 @@
         <v>85</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4021,7 +4015,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>236</v>
@@ -4132,7 +4126,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>55</v>
@@ -4312,7 +4306,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4377,7 +4371,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>116</v>
@@ -4400,7 +4394,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>116</v>
@@ -4423,7 +4417,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>116</v>
@@ -4446,7 +4440,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>116</v>
@@ -4469,7 +4463,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>116</v>
@@ -4492,7 +4486,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>116</v>
@@ -4532,19 +4526,19 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
@@ -4561,7 +4555,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>116</v>
@@ -4584,7 +4578,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>116</v>
@@ -4607,7 +4601,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>116</v>
@@ -4630,7 +4624,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>116</v>
@@ -4642,191 +4636,168 @@
         <v>7</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>420</v>
+        <v>329</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>332</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>130</v>
+        <v>333</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>391</v>
+        <v>188</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="39" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>338</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>208</v>
+        <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>343</v>
+        <v>7</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>344</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="26" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5044,7 +5015,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>78</v>
@@ -5270,7 +5241,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>100</v>
@@ -5311,10 +5282,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>100</v>
@@ -5334,7 +5305,7 @@
         <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>103</v>
@@ -5354,7 +5325,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>111</v>
@@ -5377,7 +5348,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>116</v>
@@ -5400,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>116</v>
@@ -5423,7 +5394,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>116</v>
@@ -5446,7 +5417,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>116</v>
@@ -5469,7 +5440,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>116</v>
@@ -5509,21 +5480,21 @@
     </row>
     <row r="13" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>116</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5582,7 +5553,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>133</v>
@@ -5623,10 +5594,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>133</v>
@@ -5752,7 +5723,7 @@
     </row>
     <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
@@ -5762,11 +5733,11 @@
         <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
